--- a/docs/テストケース/単体テストケース・結果一覧表_API_30分値一覧取得.xlsx
+++ b/docs/テストケース/単体テストケース・結果一覧表_API_30分値一覧取得.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単体テストケース・結果一覧表" sheetId="1" r:id="Rfaad66d12e6c48e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="権限マトリクス" sheetId="2" r:id="R533ea903a6544cc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件マトリクス" sheetId="3" r:id="Rc07f48b08c07498a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提・実施方針" sheetId="4" r:id="Raa2b654966e24e6c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="単体テストケース・結果一覧表" sheetId="1" r:id="R403c0a7da8614147"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="権限マトリクス" sheetId="2" r:id="R12cf3b9a50de4227"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="条件マトリクス" sheetId="3" r:id="Rb368f0c704a64eb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="前提・実施方針" sheetId="4" r:id="R8f990ac9027a4be5"/>
   </x:sheets>
   <x:definedNames>
     <x:definedName name="_xlnm.Print_Area" localSheetId="0">'単体テストケース・結果一覧表'!$A$1:$O$50</x:definedName>
@@ -433,7 +433,7 @@
         <x:v>備　考</x:v>
       </x:c>
       <x:c r="G5" s="6" t="str">
-        <x:v>結果欄は未実施のため空欄。複数条件は補助シートに個別結果を記入。静的解析・実施条件は「前提・実施方針」を参照。</x:v>
+        <x:v>結果欄は試験実施後に記入する。複数の条件は補助シートに個別の結果を記録する。静的解析と実施条件は「前提・実施方針」を参照する。</x:v>
       </x:c>
       <x:c r="H5" s="6"/>
       <x:c r="I5" s="6"/>
@@ -525,7 +525,7 @@
         <x:v>EP管理者／担当者</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>許可された2ロールで正常取得する。</x:v>
+        <x:v>許可された2つのロールで正常に取得できることを確認する。</x:v>
       </x:c>
       <x:c r="E8" s="10" t="n">
         <x:v>2</x:v>
@@ -534,12 +534,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G8" s="6" t="str">
-        <x:v>①D01を準備。
-②R01・R02で正規ログインした各認証情報を使用してQ0をGET。
-③権限マトリクスに結果記録。</x:v>
+        <x:v>①D01の試験データを用意する。②R01とR02でそれぞれ正規にログインし、各認証情報でQ0へGETリクエストを送る。③結果を権限マトリクスに記録する。</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
-        <x:v>各HTTP 200。result.upload_historyにD01の1行。</x:v>
+        <x:v>どちらもHTTP 200を返し、result.upload_historyにはD01に対応する1行が入る。</x:v>
       </x:c>
       <x:c r="I8" s="10" t="str"/>
       <x:c r="J8" s="10" t="str"/>
@@ -571,11 +569,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G9" s="6" t="str">
-        <x:v>①D01を準備。
-②R03～R08でQ0をGET。必要なユーザー情報は共通認証処理のスタブで設定。</x:v>
+        <x:v>①D01の試験データを用意する。②R03～R08でQ0へGETリクエストを送る。必要なユーザー情報は共通認証処理のスタブに設定する。</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
-        <x:v>各HTTP 403、message=利用権限がありません。サービス／DB照会は呼び出されない。</x:v>
+        <x:v>いずれもHTTP 403を返し、messageは「利用権限がありません」となる。サービスとDB照会は呼び出されない。</x:v>
       </x:c>
       <x:c r="I9" s="10" t="str"/>
       <x:c r="J9" s="10" t="str"/>
@@ -609,11 +606,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G10" s="6" t="str">
-        <x:v>①認証後コンテキストのorg_type_code=01、role=9／nullを順に設定。
-②Q0をGET。条件マトリクスA03に記録。</x:v>
+        <x:v>①認証後のコンテキストをorg_type_code=01にし、roleを9とnullに順次設定する。②各条件でQ0へGETリクエストを送り、条件マトリクスA03に記録する。</x:v>
       </x:c>
       <x:c r="H10" s="6" t="str">
-        <x:v>各HTTP 403。30分値を返さない。</x:v>
+        <x:v>どちらもHTTP 403を返し、30分値は返されない。</x:v>
       </x:c>
       <x:c r="I10" s="10" t="str"/>
       <x:c r="J10" s="10" t="str"/>
@@ -645,10 +641,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G11" s="6" t="str">
-        <x:v>①JWT CookieとAuthorizationを除去したクライアントでQ0をGET。</x:v>
+        <x:v>①JWT CookieとAuthorizationを付けずに、Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H11" s="6" t="str">
-        <x:v>HTTP 401。業務データを返さない。</x:v>
+        <x:v>HTTP 401を返し、業務データは返されない。</x:v>
       </x:c>
       <x:c r="I11" s="10" t="str"/>
       <x:c r="J11" s="10" t="str"/>
@@ -680,11 +676,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G12" s="6" t="str">
-        <x:v>①正規ログインで得たrefreshトークンを、一覧取得の認証トークンに指定。
-②Q0をGET。</x:v>
+        <x:v>①正規ログインで得たrefreshトークンを、一覧取得用の認証トークンとして指定する。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H12" s="6" t="str">
-        <x:v>API仕様のJWTエラーとしてHTTP 401。共通JWT処理の実応答との差があれば欠陥記録。</x:v>
+        <x:v>API仕様に従ってJWTエラーのHTTP 401を返す。共通JWT処理の実際の応答と異なる場合は欠陥として記録する。</x:v>
       </x:c>
       <x:c r="I12" s="10" t="str"/>
       <x:c r="J12" s="10" t="str"/>
@@ -707,7 +702,7 @@
         <x:v>期限切れ</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>期限切れaccessトークンで取得しない。</x:v>
+        <x:v>期限切れのaccessトークンが拒否されることを確認する。</x:v>
       </x:c>
       <x:c r="E13" s="10" t="n">
         <x:v>1</x:v>
@@ -716,11 +711,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
-        <x:v>①テスト認証基盤で期限切れaccessトークンを発行。
-②自動refreshを行わないHTTPクライアントでQ0をGET。</x:v>
+        <x:v>①テスト認証基盤で期限切れのaccessトークンを発行する。②自動refreshを行わないHTTPクライアントでQ0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H13" s="6" t="str">
-        <x:v>HTTP 401。業務データを返さない。</x:v>
+        <x:v>HTTP 401を返し、業務データは返されない。</x:v>
       </x:c>
       <x:c r="I13" s="10" t="str"/>
       <x:c r="J13" s="10" t="str"/>
@@ -752,12 +746,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
-        <x:v>①D01を準備。
-②本文なしでQ0をGET。
-③サービスに渡る辞書をデバッガで確認。</x:v>
+        <x:v>①D01の試験データを用意する。②本文を付けずにQ0へGETリクエストを送る。③サービスに渡された辞書をデバッガで確認する。</x:v>
       </x:c>
       <x:c r="H14" s="6" t="str">
-        <x:v>corp_number=C1、building_id=B20、agreement_category=01、org_id=O1の実値を受け取る。</x:v>
+        <x:v>corp_numberにはC1、building_idにはB20、agreement_categoryには01、org_idにはO1の実値が渡される。</x:v>
       </x:c>
       <x:c r="I14" s="10" t="str"/>
       <x:c r="J14" s="10" t="str"/>
@@ -789,11 +781,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
-        <x:v>①D01と、法人番号だけC2に変えた別行・対応建物を準備。
-②Q0をGET。</x:v>
+        <x:v>①D01と、法人番号だけをC2に変えた別の生データ行および対応建物を用意する。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H15" s="6" t="str">
-        <x:v>D01の1行のみ。C2を集計しない。</x:v>
+        <x:v>D01に対応する1行だけを返し、C2のデータは集計されない。</x:v>
       </x:c>
       <x:c r="I15" s="10" t="str"/>
       <x:c r="J15" s="10" t="str">
@@ -827,11 +818,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G16" s="6" t="str">
-        <x:v>①D01と、区分02・取得日20260131の行と対応建物を追加。
-②Q0をGET。</x:v>
+        <x:v>①D01に加え、同意区分02・取得日20260131の生データ行と対応建物を用意する。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H16" s="6" t="str">
-        <x:v>period_to=20260104。区分02の20260131を含めない。</x:v>
+        <x:v>period_toは20260104となり、区分02の20260131は集計に含まれない。</x:v>
       </x:c>
       <x:c r="I16" s="10" t="str"/>
       <x:c r="J16" s="10" t="str">
@@ -865,11 +855,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G17" s="6" t="str">
-        <x:v>①D01のみ準備。
-②corp_number=C2に変更してGET。</x:v>
+        <x:v>①D01だけを用意する。②corp_numberをC2に変えてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H17" s="6" t="str">
-        <x:v>HTTP 200、result.upload_history=[]。</x:v>
+        <x:v>HTTP 200を返し、result.upload_historyは空配列になる。</x:v>
       </x:c>
       <x:c r="I17" s="10" t="str"/>
       <x:c r="J17" s="10" t="str"/>
@@ -901,11 +890,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G18" s="6" t="str">
-        <x:v>①D01＋D02。
-②Q0をGET。</x:v>
+        <x:v>①D01とD02を用意する。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H18" s="6" t="str">
-        <x:v>B20の1行のみ。B10を返さない。</x:v>
+        <x:v>B20に対応する1行だけを返し、B10の行は返されない。</x:v>
       </x:c>
       <x:c r="I18" s="10" t="str"/>
       <x:c r="J18" s="10" t="str">
@@ -939,11 +927,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
-        <x:v>①D01＋D02。
-②building_id=空文字でGET。</x:v>
+        <x:v>①D01とD02を用意する。②building_idを空文字にしてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H19" s="6" t="str">
-        <x:v>2行。B20の期間02～04、B10の期間03～03。</x:v>
+        <x:v>B20の期間02～04とB10の期間03～03に対応する2行を返す。</x:v>
       </x:c>
       <x:c r="I19" s="10" t="str"/>
       <x:c r="J19" s="10" t="str"/>
@@ -975,11 +962,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
-        <x:v>①D01＋D02。
-②building_idキーを付けずGET。</x:v>
+        <x:v>①D01とD02を用意する。②building_idをクエリから省いてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H20" s="6" t="str">
-        <x:v>空文字と同じ2行。</x:v>
+        <x:v>building_idを空文字にした場合と同じ2行を返す。</x:v>
       </x:c>
       <x:c r="I20" s="10" t="str"/>
       <x:c r="J20" s="10" t="str"/>
@@ -991,7 +977,7 @@
       <x:c r="N20" s="10" t="str"/>
       <x:c r="O20" s="10" t="str"/>
     </x:row>
-    <x:row r="21" ht="87.5" customHeight="1">
+    <x:row r="21" ht="75" customHeight="1">
       <x:c r="A21" s="10" t="n">
         <x:v>14</x:v>
       </x:c>
@@ -1011,12 +997,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
-        <x:v>①D01の建物はorg_id=O1、agreement_org=O2。
-②別拠点B10はorg_id=O2、agreement_org=O1。
-③building_id空欄、org_id=O1でGET。</x:v>
+        <x:v>①D01の建物にorg_id=O1、agreement_org=O2を設定する。②別拠点B10にはorg_id=O2、agreement_org=O1を設定する。③building_idを空文字、org_idをO1にしてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H21" s="6" t="str">
-        <x:v>B20だけを返す。agreement_orgがO1のB10は対象にしない。</x:v>
+        <x:v>B20だけを返す。agreement_orgがO1でも、org_idがO2のB10は対象にならない。</x:v>
       </x:c>
       <x:c r="I21" s="10" t="str"/>
       <x:c r="J21" s="10" t="str">
@@ -1050,11 +1034,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
-        <x:v>①前ケースと同じ2拠点を独立に準備。
-②building_idとorg_idを空文字でGET。</x:v>
+        <x:v>①前のケースと同じ2拠点を、独立した条件として用意する。②building_idとorg_idを空文字にしてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H22" s="6" t="str">
-        <x:v>B20とB10の2行。</x:v>
+        <x:v>B20とB10に対応する2行を返す。</x:v>
       </x:c>
       <x:c r="I22" s="10" t="str"/>
       <x:c r="J22" s="10" t="str"/>
@@ -1086,11 +1069,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
-        <x:v>①D01＋org_id=O2のD02。
-②building_id空欄、org_idキー省略でGET。</x:v>
+        <x:v>①D01と、org_idがO2のD02を用意する。②building_idを空文字にし、org_idをクエリから省いてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H23" s="6" t="str">
-        <x:v>B20とB10の2行。</x:v>
+        <x:v>B20とB10に対応する2行を返す。</x:v>
       </x:c>
       <x:c r="I23" s="10" t="str"/>
       <x:c r="J23" s="10" t="str"/>
@@ -1113,7 +1095,7 @@
         <x:v>組織ID該当なし</x:v>
       </x:c>
       <x:c r="D24" s="6" t="str">
-        <x:v>存在しない組織で取得しない。</x:v>
+        <x:v>指定した組織にデータがない場合の応答を確認する。</x:v>
       </x:c>
       <x:c r="E24" s="10" t="n">
         <x:v>1</x:v>
@@ -1122,11 +1104,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
-        <x:v>①D01のみ。
-②org_id=O2でGET。</x:v>
+        <x:v>①D01だけを用意する。②org_idをO2にしてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H24" s="6" t="str">
-        <x:v>HTTP 200、result.upload_history=[]。</x:v>
+        <x:v>HTTP 200を返し、result.upload_historyは空配列になる。</x:v>
       </x:c>
       <x:c r="I24" s="10" t="str"/>
       <x:c r="J24" s="10" t="str"/>
@@ -1158,11 +1139,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G25" s="6" t="str">
-        <x:v>①条件マトリクスA18のデータを準備。
-②同表の4クエリを実行し各結果を記録。</x:v>
+        <x:v>①条件マトリクスA18に記載したデータを用意する。②同表の4種類のクエリを送信し、それぞれの結果を記録する。</x:v>
       </x:c>
       <x:c r="H25" s="6" t="str">
-        <x:v>同表の期待ID集合と一致し、各条件を独立に省略できる。</x:v>
+        <x:v>各応答の拠点IDは条件マトリクスの期待値と一致する。拠点IDと組織IDはそれぞれ独立に省略できる。</x:v>
       </x:c>
       <x:c r="I25" s="10" t="str"/>
       <x:c r="J25" s="10" t="str">
@@ -1196,11 +1176,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G26" s="6" t="str">
-        <x:v>①D01に20260131、delete_flg=TRUEの行を追加。
-②Q0をGET。</x:v>
+        <x:v>①D01に、取得日20260131・delete_flg=TRUEの生データ行を追加する。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H26" s="6" t="str">
-        <x:v>期間は20260102～20260104。削除行のARVE値・日時も集計に入らない。</x:v>
+        <x:v>期間は20260102～20260104のままである。削除済み行のARVE値と日時も集計に含まれない。</x:v>
       </x:c>
       <x:c r="I26" s="10" t="str"/>
       <x:c r="J26" s="10" t="str">
@@ -1234,11 +1213,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G27" s="6" t="str">
-        <x:v>①D01の生データ2行をdelete_flg=NULLに変更。
-②Q0をGET。</x:v>
+        <x:v>①D01の生データ2行のdelete_flgをNULLにする。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H27" s="6" t="str">
-        <x:v>API設計書のSQL例「IS NOT true」に従いD01が返る。FALSEのみとする表記との相違は実施方針の確認事項に記載。</x:v>
+        <x:v>API設計書のSQL例「IS NOT true」に従い、D01が返される。「FALSEのみ」とする表記との相違は、実施方針の確認事項に記録する。</x:v>
       </x:c>
       <x:c r="I27" s="10" t="str"/>
       <x:c r="J27" s="10" t="str">
@@ -1272,11 +1250,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G28" s="6" t="str">
-        <x:v>①D01の建物delete_flgをTRUEにしてGET。
-②NULLにしてGET。条件マトリクスA21へ記録。</x:v>
+        <x:v>①D01の建物のdelete_flgをTRUEにしてGETリクエストを送る。②同じ値をNULLにして再度送る。③各結果を条件マトリクスA21に記録する。</x:v>
       </x:c>
       <x:c r="H28" s="6" t="str">
-        <x:v>各HTTP 200、空配列。有効建物はdelete_flg=FALSEに限定する。</x:v>
+        <x:v>どちらもHTTP 200を返し、結果は空配列になる。有効な建物はdelete_flg=FALSEの行に限られる。</x:v>
       </x:c>
       <x:c r="I28" s="10" t="str"/>
       <x:c r="J28" s="10" t="str">
@@ -1310,12 +1287,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G29" s="6" t="str">
-        <x:v>①D01の生データを保持。
-②建物のcorporate_numberをC2に変更し、元の対応建物を除く。
-③Q0をGET。</x:v>
+        <x:v>①D01の生データを保持する。②建物のcorporate_numberをC2に変え、元の対応建物を除く。③Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H29" s="6" t="str">
-        <x:v>空配列。他の2キーが同じでも誤結合しない。</x:v>
+        <x:v>結果は空配列になる。他の2つの結合キーが一致していても、誤って結合されない。</x:v>
       </x:c>
       <x:c r="I29" s="10" t="str"/>
       <x:c r="J29" s="10" t="str">
@@ -1349,12 +1324,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G30" s="6" t="str">
-        <x:v>①D01の生データを保持。
-②建物のagreement_categoryを02に変更し、元の対応建物を除く。
-③Q0をGET。</x:v>
+        <x:v>①D01の生データを保持する。②建物のagreement_categoryを02に変え、元の対応建物を除く。③Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H30" s="6" t="str">
-        <x:v>空配列。他の2キーが同じでも誤結合しない。</x:v>
+        <x:v>結果は空配列になる。他の2つの結合キーが一致していても、誤って結合されない。</x:v>
       </x:c>
       <x:c r="I30" s="10" t="str"/>
       <x:c r="J30" s="10" t="str">
@@ -1388,12 +1361,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G31" s="6" t="str">
-        <x:v>①D01の生データを保持。
-②建物のbuilding_idをB10に変更し、元の対応建物を除く。
-③Q0をGET。</x:v>
+        <x:v>①D01の生データを保持する。②建物のbuilding_idをB10に変え、元の対応建物を除く。③Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H31" s="6" t="str">
-        <x:v>空配列。他の2キーが同じでも誤結合しない。</x:v>
+        <x:v>結果は空配列になる。他の2つの結合キーが一致していても、誤って結合されない。</x:v>
       </x:c>
       <x:c r="I31" s="10" t="str"/>
       <x:c r="J31" s="10" t="str">
@@ -1427,11 +1398,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G32" s="6" t="str">
-        <x:v>①D01の生データを保持し、対応建物を検証DBから除く。
-②Q0をGET。</x:v>
+        <x:v>①D01の生データを保持し、対応建物を検証用DBから除く。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H32" s="6" t="str">
-        <x:v>空配列。生データだけで一覧に載らない。</x:v>
+        <x:v>結果は空配列になる。対応する建物がない生データは一覧に表示されない。</x:v>
       </x:c>
       <x:c r="I32" s="10" t="str"/>
       <x:c r="J32" s="10" t="str">
@@ -1465,11 +1435,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G33" s="6" t="str">
-        <x:v>①D01の建物をorg_id=O2でも追加。
-②org_id空欄でQ0をGET。</x:v>
+        <x:v>①D01に対応する建物を、org_id=O2でも追加する。②org_idを空文字にしてQ0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H33" s="6" t="str">
-        <x:v>D01の1行だけ。EXISTSで件数が倍増しない。</x:v>
+        <x:v>D01に対応する1行だけを返す。複数の建物が一致しても、EXISTS結合で行数は増えない。</x:v>
       </x:c>
       <x:c r="I33" s="10" t="str"/>
       <x:c r="J33" s="10" t="str">
@@ -1503,11 +1472,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G34" s="6" t="str">
-        <x:v>①D01の20260102行だけ準備。
-②Q0をGET。</x:v>
+        <x:v>①D01から取得日20260102の生データ1行だけを用意する。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H34" s="6" t="str">
-        <x:v>1行、period_from=period_to=20260102。</x:v>
+        <x:v>1行を返し、period_fromとperiod_toはいずれも20260102になる。</x:v>
       </x:c>
       <x:c r="I34" s="10" t="str"/>
       <x:c r="J34" s="10" t="str">
@@ -1521,7 +1489,7 @@
       <x:c r="N34" s="10" t="str"/>
       <x:c r="O34" s="10" t="str"/>
     </x:row>
-    <x:row r="35" ht="65" customHeight="1">
+    <x:row r="35" ht="75" customHeight="1">
       <x:c r="A35" s="10" t="n">
         <x:v>28</x:v>
       </x:c>
@@ -1541,11 +1509,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G35" s="6" t="str">
-        <x:v>①D01の2日分を逆順で投入。20260103は置かない。
-②Q0をGET。</x:v>
+        <x:v>①D01の2日分の生データを逆順に登録し、20260103のデータは用意しない。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H35" s="6" t="str">
-        <x:v>1行、period_from=20260102、period_to=20260104。欠日の有無で期間を分割しない。</x:v>
+        <x:v>1行を返し、period_fromは20260102、period_toは20260104になる。途中の日付が欠けていても期間は分割されない。</x:v>
       </x:c>
       <x:c r="I35" s="10" t="str"/>
       <x:c r="J35" s="10" t="str">
@@ -1559,7 +1526,7 @@
       <x:c r="N35" s="10" t="str"/>
       <x:c r="O35" s="10" t="str"/>
     </x:row>
-    <x:row r="36" ht="65" customHeight="1">
+    <x:row r="36" ht="75" customHeight="1">
       <x:c r="A36" s="10" t="n">
         <x:v>29</x:v>
       </x:c>
@@ -1579,11 +1546,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G36" s="6" t="str">
-        <x:v>①D01＋D02。
-②building_id空欄でGET。</x:v>
+        <x:v>①D01とD02を用意する。②building_idを空文字にしてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H36" s="6" t="str">
-        <x:v>2行。B20は02～04、B10は03～03。各行の法人番号・拠点名・拠点IDが元データと一致。</x:v>
+        <x:v>B20の期間02～04とB10の期間03～03に対応する2行を返す。各行の法人番号・拠点名・拠点IDは元データと一致する。</x:v>
       </x:c>
       <x:c r="I36" s="10" t="str"/>
       <x:c r="J36" s="10" t="str">
@@ -1597,7 +1563,7 @@
       <x:c r="N36" s="10" t="str"/>
       <x:c r="O36" s="10" t="str"/>
     </x:row>
-    <x:row r="37" ht="65" customHeight="1">
+    <x:row r="37" ht="75" customHeight="1">
       <x:c r="A37" s="10" t="n">
         <x:v>30</x:v>
       </x:c>
@@ -1617,11 +1583,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G37" s="6" t="str">
-        <x:v>①D01を準備。file_update_dateは全行2025-12-01に設定。
-②Q0をGET。</x:v>
+        <x:v>①D01を用意し、元テーブルの全行のfile_update_dateを2025-12-01に設定する。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H37" s="6" t="str">
-        <x:v>file_update_date（応答）=2026-01-05 10:20:30。元テーブルのfile_update_dateの値とは区別。</x:v>
+        <x:v>応答のfile_update_dateは2026-01-05 10:20:30になる。元テーブルのfile_update_dateとは別の値として確認する。</x:v>
       </x:c>
       <x:c r="I37" s="10" t="str"/>
       <x:c r="J37" s="10" t="str">
@@ -1655,11 +1620,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G38" s="6" t="str">
-        <x:v>①D01の20260102行のみ、updated_at=NULL、created_at=2026-01-03 04:05:06。
-②Q0をGET。</x:v>
+        <x:v>①D01の20260102の行だけを用意し、updated_atをNULL、created_atを2026-01-03 04:05:06にする。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H38" s="6" t="str">
-        <x:v>file_update_date=2026-01-03 04:05:06。実装補足の回帰確認。</x:v>
+        <x:v>file_update_dateは2026-01-03 04:05:06になる。実装上の日時補完処理を確認する。</x:v>
       </x:c>
       <x:c r="I38" s="10" t="str"/>
       <x:c r="J38" s="10" t="str">
@@ -1693,11 +1657,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G39" s="6" t="str">
-        <x:v>①D01の両日時を明示的にNULLへ更新。
-②Q0をGET。</x:v>
+        <x:v>①D01のcreated_atとupdated_atを、どちらも明示的にNULLにする。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H39" s="6" t="str">
-        <x:v>1行を返しfile_update_date=null。例外や文字列「None」にならない。</x:v>
+        <x:v>1行を返し、file_update_dateはJSONのnullになる。例外は発生せず、「None」という文字列にもならない。</x:v>
       </x:c>
       <x:c r="I39" s="10" t="str"/>
       <x:c r="J39" s="10" t="str">
@@ -1711,7 +1674,7 @@
       <x:c r="N39" s="10" t="str"/>
       <x:c r="O39" s="10" t="str"/>
     </x:row>
-    <x:row r="40" ht="75" customHeight="1">
+    <x:row r="40" ht="87.5" customHeight="1">
       <x:c r="A40" s="10" t="n">
         <x:v>33</x:v>
       </x:c>
@@ -1731,11 +1694,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G40" s="6" t="str">
-        <x:v>①D01を準備。
-②Q0のJSONを保存し、DBのARVE3項目と照合。</x:v>
+        <x:v>①D01を用意する。②Q0のJSON応答を保存し、DBのARVEの3項目と比較する。</x:v>
       </x:c>
       <x:c r="H40" s="6" t="str">
-        <x:v>ARVE_CORP_NAME=ARVE試験会社、ARVE_OFFICE_CODE=012、ARVE_CUSTOMER_NUMBER=0000000000045。値と物理名が一致。</x:v>
+        <x:v>ARVE_CORP_NAMEは「ARVE試験会社」、ARVE_OFFICE_CODEは「012」、ARVE_CUSTOMER_NUMBERは「0000000000045」になる。キー名と値の対応はDBと一致する。</x:v>
       </x:c>
       <x:c r="I40" s="10" t="str"/>
       <x:c r="J40" s="10" t="str">
@@ -1749,7 +1711,7 @@
       <x:c r="N40" s="10" t="str"/>
       <x:c r="O40" s="10" t="str"/>
     </x:row>
-    <x:row r="41" ht="65" customHeight="1">
+    <x:row r="41" ht="75" customHeight="1">
       <x:c r="A41" s="10" t="n">
         <x:v>34</x:v>
       </x:c>
@@ -1769,11 +1731,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G41" s="6" t="str">
-        <x:v>①D01のARVE3項目を全行NULL／全行空文字にして各GET。
-②条件マトリクスA34へ結果記録。</x:v>
+        <x:v>①D01の全行についてARVEの3項目をNULLにしてGETリクエストを送る。②3項目を空文字にして再度送る。③各結果を条件マトリクスA34に記録する。</x:v>
       </x:c>
       <x:c r="H41" s="6" t="str">
-        <x:v>NULL条件はJSON null、空文字条件は空文字を返す。キーは常に存在する。</x:v>
+        <x:v>NULLの条件では3つのキーがすべてJSONのnullになり、空文字の条件ではすべて空文字になる。どちらの条件でもキーは存在する。</x:v>
       </x:c>
       <x:c r="I41" s="10" t="str"/>
       <x:c r="J41" s="10" t="str">
@@ -1787,7 +1748,7 @@
       <x:c r="N41" s="10" t="str"/>
       <x:c r="O41" s="10" t="str"/>
     </x:row>
-    <x:row r="42" ht="87.5" customHeight="1">
+    <x:row r="42" ht="100" customHeight="1">
       <x:c r="A42" s="10" t="n">
         <x:v>35</x:v>
       </x:c>
@@ -1807,11 +1768,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G42" s="6" t="str">
-        <x:v>①D01を準備。
-②JSONのキー・型・値を保存。</x:v>
+        <x:v>①D01を用意する。②JSON応答のキー名、型、値を保存する。</x:v>
       </x:c>
       <x:c r="H42" s="6" t="str">
-        <x:v>法人番号、拠点ID、period_from/period_to、ARVEコード・番号は文字列。012・0000000000045のゼロを保持。日時はYYYY-MM-DD HH:mm:ss。</x:v>
+        <x:v>法人番号、拠点ID、period_from、period_to、ARVEコード、ARVE番号はいずれも文字列になる。「012」と「0000000000045」の先頭のゼロは保持され、日時はYYYY-MM-DD HH:mm:ss形式になる。</x:v>
       </x:c>
       <x:c r="I42" s="10" t="str"/>
       <x:c r="J42" s="10" t="str"/>
@@ -1843,11 +1803,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G43" s="6" t="str">
-        <x:v>①D01（B20／A拠点）＋D02（B10／B拠点）。
-②building_id空欄でGET。</x:v>
+        <x:v>①D01をB20／A拠点、D02をB10／B拠点として用意する。②building_idを空文字にしてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H43" s="6" t="str">
-        <x:v>設計書の指定どおりA拠点(B20)→B拠点(B10)の順。ID順になった場合は欠陥として記録する。</x:v>
+        <x:v>設計書の指定どおり、A拠点（B20）、B拠点（B10）の順に返す。拠点ID順になった場合は欠陥として記録する。</x:v>
       </x:c>
       <x:c r="I43" s="10" t="str"/>
       <x:c r="J43" s="10" t="str">
@@ -1881,11 +1840,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G44" s="6" t="str">
-        <x:v>①2拠点とも拠点名=A拠点。B20の開始日20260101、B10の開始日20260201。
-②building_id空欄でGET。</x:v>
+        <x:v>①2拠点の名前をどちらもA拠点にする。開始日はB20を20260101、B10を20260201にする。②building_idを空文字にしてGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H44" s="6" t="str">
-        <x:v>B20→B10の開始日昇順。「データ項目更新仕様説明書」ソート順欄を基準とする。</x:v>
+        <x:v>B20、B10の順に開始日が昇順で返される。「データ項目更新仕様説明書」のソート順欄を基準とする。</x:v>
       </x:c>
       <x:c r="I44" s="10" t="str"/>
       <x:c r="J44" s="10" t="str">
@@ -1919,11 +1877,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G45" s="6" t="str">
-        <x:v>①D01の建物のみ準備。
-②生データ0件でQ0をGET。</x:v>
+        <x:v>①D01の建物だけを用意し、生データは0件にする。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H45" s="6" t="str">
-        <x:v>HTTP 200、result.upload_history=[]。エラー扱いしない。</x:v>
+        <x:v>HTTP 200を返し、result.upload_historyは空配列になる。0件をエラーとして扱わない。</x:v>
       </x:c>
       <x:c r="I45" s="10" t="str"/>
       <x:c r="J45" s="10" t="str"/>
@@ -1957,12 +1914,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G46" s="6" t="str">
-        <x:v>①D01の生データ・建物をダンプ。
-②Q0をGET。
-③同じ対象のダンプを比較。</x:v>
+        <x:v>①D01の生データと建物のダンプを保存する。②Q0へGETリクエストを送る。③同じ対象のダンプを再び取得して比較する。</x:v>
       </x:c>
       <x:c r="H46" s="6" t="str">
-        <x:v>行数・業務項目・監査項目が一致。INSERT/UPDATE/DELETEを発行しない。</x:v>
+        <x:v>前後の行数、業務項目、監査項目は一致する。INSERT、UPDATE、DELETEは発行されない。</x:v>
       </x:c>
       <x:c r="I46" s="10" t="str"/>
       <x:c r="J46" s="10" t="str">
@@ -1976,7 +1931,7 @@
       <x:c r="N46" s="10" t="str"/>
       <x:c r="O46" s="10" t="str"/>
     </x:row>
-    <x:row r="47" ht="65" customHeight="1">
+    <x:row r="47" ht="87.5" customHeight="1">
       <x:c r="A47" s="10" t="n">
         <x:v>40</x:v>
       </x:c>
@@ -1996,11 +1951,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G47" s="6" t="str">
-        <x:v>①ローカルテスト環境でsession生成を接続例外にする。
-②Q0をGETし、HTTPとログを取得。</x:v>
+        <x:v>①ローカルテスト環境でセッション生成時にDB接続例外を発生させる。②Q0へGETリクエストを送り、HTTP応答とログを保存する。</x:v>
       </x:c>
       <x:c r="H47" s="6" t="str">
-        <x:v>HTTP 500、message=システムエラーが発生しました。取得失敗のERRORログ。200の空配列を返さない。</x:v>
+        <x:v>HTTP 500を返し、messageは「システムエラーが発生しました。」になる。取得失敗を示すERRORログが残り、HTTP 200の空配列は返されない。</x:v>
       </x:c>
       <x:c r="I47" s="10" t="str"/>
       <x:c r="J47" s="10" t="str"/>
@@ -2034,12 +1988,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G48" s="6" t="str">
-        <x:v>①接続後のquery.allをDB例外にする。
-②Q0をGET。
-③例外設定を解除し同じ接続管理で再度GET。</x:v>
+        <x:v>①DB接続後のquery.allで例外を発生させる。②Q0へGETリクエストを送る。③例外設定を解除し、同じ接続管理を使って再度GETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H48" s="6" t="str">
-        <x:v>1回目500と指定メッセージ、ERRORログ。2回目は200。失敗セッションが残って後続処理を妨げない。</x:v>
+        <x:v>1回目はHTTP 500と指定のメッセージを返し、ERRORログが残る。2回目はHTTP 200を返し、失敗したセッションが後続処理を妨げない。</x:v>
       </x:c>
       <x:c r="I48" s="10" t="str"/>
       <x:c r="J48" s="10" t="str"/>
@@ -2073,10 +2025,10 @@
         <x:v>異常</x:v>
       </x:c>
       <x:c r="G49" s="6" t="str">
-        <x:v>①サービス呼出しをRuntimeErrorへ差し替えQ0をGET。</x:v>
+        <x:v>①サービス呼び出しをRuntimeErrorが発生するように差し替える。②Q0へGETリクエストを送る。</x:v>
       </x:c>
       <x:c r="H49" s="6" t="str">
-        <x:v>HTTP 500、指定のシステムエラーメッセージ。内部例外の詳細をレスポンスへ漏らさずログへ記録。</x:v>
+        <x:v>HTTP 500と指定のシステムエラーメッセージを返す。内部例外の詳細は応答に含まれず、ログに記録される。</x:v>
       </x:c>
       <x:c r="I49" s="10" t="str"/>
       <x:c r="J49" s="10" t="str"/>
@@ -2090,7 +2042,7 @@
       <x:c r="N49" s="10" t="str"/>
       <x:c r="O49" s="10" t="str"/>
     </x:row>
-    <x:row r="50" ht="75" customHeight="1">
+    <x:row r="50" ht="87.5" customHeight="1">
       <x:c r="A50" s="10" t="n">
         <x:v>43</x:v>
       </x:c>
@@ -2110,12 +2062,10 @@
         <x:v>正常</x:v>
       </x:c>
       <x:c r="G50" s="6" t="str">
-        <x:v>①D01で正常GET。
-②DB例外で異常GET。
-③条件マトリクスA43にログファイルと時刻を記録。</x:v>
+        <x:v>①D01で正常なGETリクエストを送る。②DB例外を発生させて異常なGETリクエストを送る。③ログファイルと実施時刻を条件マトリクスA43に記録する。</x:v>
       </x:c>
       <x:c r="H50" s="6" t="str">
-        <x:v>正常は開始・終了のINFO。異常はERRORと終了記録。対象APIのリクエスト時刻と対応し、異常を成功と記録しない。</x:v>
+        <x:v>正常時は開始と終了がINFOで記録される。異常時はERRORと終了が記録され、対象APIのリクエスト時刻と対応する。異常な処理が成功として記録されない。</x:v>
       </x:c>
       <x:c r="I50" s="10" t="str"/>
       <x:c r="J50" s="10" t="str"/>
@@ -2471,10 +2421,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C4" s="6" t="str">
-        <x:v>org_type_code=01／role=9</x:v>
+        <x:v>org_type_codeを01、roleを9にする。</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>HTTP 403。</x:v>
+        <x:v>HTTP 403を返す。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str"/>
       <x:c r="F4" s="6" t="str"/>
@@ -2488,10 +2438,10 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>org_type_code=01／role=null</x:v>
+        <x:v>org_type_codeを01、roleをnullにする。</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>HTTP 403。</x:v>
+        <x:v>HTTP 403を返す。</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str"/>
       <x:c r="F5" s="6" t="str"/>
@@ -2505,10 +2455,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>D01: B20/O1、D02: B10/O2。リクエスト building_id=B20、org_id=O1</x:v>
+        <x:v>D01をB20／O1、D02をB10／O2にし、building_id=B20、org_id=O1で送る。</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>B20のみ</x:v>
+        <x:v>B20に対応する行だけを返す。</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str"/>
       <x:c r="F6" s="6" t="str"/>
@@ -2522,10 +2472,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C7" s="6" t="str">
-        <x:v>D01: B20/O1、D02: B10/O2。リクエスト building_id=B20、org_id=空文字</x:v>
+        <x:v>D01をB20／O1、D02をB10／O2にし、building_id=B20、org_idを空文字で送る。</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>B20のみ</x:v>
+        <x:v>B20に対応する行だけを返す。</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str"/>
       <x:c r="F7" s="6" t="str"/>
@@ -2539,10 +2489,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
-        <x:v>D01: B20/O1、D02: B10/O2。リクエスト building_id=空文字、org_id=O1</x:v>
+        <x:v>D01をB20／O1、D02をB10／O2にし、building_idを空文字、org_id=O1で送る。</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>B20のみ</x:v>
+        <x:v>B20に対応する行だけを返す。</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str"/>
       <x:c r="F8" s="6" t="str"/>
@@ -2556,10 +2506,10 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
-        <x:v>D01: B20/O1、D02: B10/O2。リクエスト building_id=空文字、org_id=空文字</x:v>
+        <x:v>D01をB20／O1、D02をB10／O2にし、building_idとorg_idを空文字で送る。</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>B20・B10の2行</x:v>
+        <x:v>B20とB10に対応する2行を返す。</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str"/>
       <x:c r="F9" s="6" t="str"/>
@@ -2573,10 +2523,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str">
-        <x:v>建物delete_flg=TRUE</x:v>
+        <x:v>建物のdelete_flgをTRUEにする。</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>HTTP 200、空配列。</x:v>
+        <x:v>HTTP 200を返し、結果は空配列になる。</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str"/>
       <x:c r="F10" s="6" t="str"/>
@@ -2590,10 +2540,10 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
-        <x:v>建物delete_flg=NULL</x:v>
+        <x:v>建物のdelete_flgをNULLにする。</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>HTTP 200、空配列。</x:v>
+        <x:v>HTTP 200を返し、結果は空配列になる。</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str"/>
       <x:c r="F11" s="6" t="str"/>
@@ -2607,10 +2557,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
-        <x:v>生データARVE3項目=NULL</x:v>
+        <x:v>生データのARVEの3項目をすべてNULLにする。</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>3キーすべてJSON null。</x:v>
+        <x:v>JSONの3つのキーはすべてnullになる。</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str"/>
       <x:c r="F12" s="6" t="str"/>
@@ -2624,10 +2574,10 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>生データARVE3項目=空文字</x:v>
+        <x:v>生データのARVEの3項目をすべて空文字にする。</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>3キーすべて空文字。</x:v>
+        <x:v>JSONの3つのキーはすべて空文字になる。</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str"/>
       <x:c r="F13" s="6" t="str"/>
@@ -2641,10 +2591,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="C14" s="6" t="str">
-        <x:v>正常取得</x:v>
+        <x:v>正常に一覧を取得する。</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>開始／終了INFO。</x:v>
+        <x:v>処理の開始と終了がINFOログに記録される。</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str"/>
       <x:c r="F14" s="6" t="str"/>
@@ -2658,10 +2608,10 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="6" t="str">
-        <x:v>DB例外</x:v>
+        <x:v>DB例外を発生させる。</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>ERRORと終了記録。リクエストとログ時刻が対応。</x:v>
+        <x:v>ERRORと処理終了が記録され、リクエストとログの時刻が対応する。</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str"/>
       <x:c r="F15" s="6" t="str"/>
@@ -2724,7 +2674,7 @@
         <x:v>開始／完了</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>ソースレビュー・静的解析をクリアして開始。全実行条件の消化率100％、未解決欠陥0件で完了。結果・実施日・実施者は実行後に記録する。</x:v>
+        <x:v>ソースレビューと静的解析を完了してから試験を始める。すべての条件を実施し、未解決の欠陥が0件になった時点で完了とする。結果・実施日・実施者は試験後に記録する。</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="37.5" customHeight="1">
@@ -2732,7 +2682,7 @@
         <x:v>自動テスト</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>計画書でPytest・C0/C1 90％を要求する対象は指定の2バッチ。本画面／APIには一律のカバレッジ基準を設定しない。既存のPytest 2件だけで手動ケースをOKにしない。</x:v>
+        <x:v>計画書でPytestとC0/C1のカバレッジ90％以上が求められるのは、指定された2つのバッチである。この画面とAPIには一律のカバレッジ基準を設けない。既存のPytest 2件が成功しても、手動試験を完了した扱いにはしない。</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="37.5" customHeight="1">
@@ -2740,7 +2690,7 @@
         <x:v>静的解析</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>画面はESLint、バックエンドはFlake8。命名、未使用import/変数、any・型アサーション、useEffect依存、三項演算子ネスト、JSX／PEP8、行長、構文、空白、複雑度を確認。</x:v>
+        <x:v>画面ではESLint、バックエンドではFlake8を使う。命名、未使用のimport・変数、any・型アサーション、useEffectの依存関係、三項演算子の入れ子、JSX・PEP8、行の長さ、構文、空白、複雑度を確認する。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="37.5" customHeight="1">
@@ -2748,7 +2698,7 @@
         <x:v>静的解析の記録</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>実行コマンド・ツール設定・対象ファイル・実行日時・ログ保存先・STEP3ベースラインとの差分・残指摘対応を記録する。修正不可はTEPSYS協議の許容記録を残す。静的解析結果：未実施。</x:v>
+        <x:v>実行コマンド、ツールの設定、対象ファイル、実行日時、ログの保存先、STEP3時点との差分、残る指摘への対応を記録する。修正できない指摘は、TEPSYSと協議した許容記録を残す。静的解析は未実施である。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="28" customHeight="1">
@@ -2756,7 +2706,7 @@
         <x:v>STEP3との差分</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>STEP4変更前の検出内容を保持し、新規・変更箇所の差分を対象とする。既存指摘を無条件に改修対象へ含めない。</x:v>
+        <x:v>STEP4の変更前に検出された内容を保持し、新規・変更箇所との差分を確認する。既存の指摘を無条件に改修対象へ加えない。</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="37.5" customHeight="1">
@@ -2772,7 +2722,7 @@
         <x:v>証跡</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>初期表示とメッセージ表示は画面HCを取得。画面共通項目チェックは目視確認のみでHC不要。API入出力は通信記録、DB照合は対象行ダンプ、ログは実行時刻を対応させて保存。</x:v>
+        <x:v>初期表示とメッセージ表示では画面のハードコピーを取得する。画面共通項目チェックは目視で確認し、ハードコピーは不要とする。APIの入出力は通信記録、DBの照合は対象行のダンプで確認する。ログは実行時刻と対応づけて保存する。</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="37.5" customHeight="1">
@@ -2788,7 +2738,7 @@
         <x:v>データ方針</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>STEP3開発環境マスタ・受領済サンプルを優先再利用。不足するトランザクションのみ追加する。C1/C2/O1/O2/B20/B10は論理識別子であり、下の対応欄に実IDを記入してから実施する。</x:v>
+        <x:v>STEP3の開発環境マスタと受領済みのサンプルを優先して再利用し、不足するトランザクションだけを追加する。C1/C2/O1/O2/B20/B10は論理識別子なので、下の対応欄に実際のIDを記入してから試験する。</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="37.5" customHeight="1">
@@ -2796,7 +2746,7 @@
         <x:v>独立再実行</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
-        <x:v>各ケース前にD01等の指定データを再準備し、対象行の前後ダンプを採取。検証用に変更した行は保存した状態へ戻す。他ケースの実行順に依存させない。</x:v>
+        <x:v>各ケースの前にD01などの指定データを準備し、対象行の実施前後のダンプを取得する。検証のために変更した行は元の状態へ戻し、ほかのケースの実行順に依存しないようにする。</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="28" customHeight="1">
@@ -2828,7 +2778,7 @@
         <x:v>ユーザー</x:v>
       </x:c>
       <x:c r="B18" s="6" t="str">
-        <x:v>R01等の試験ユーザーID・組織・権限は権限マトリクスに記入。既存ユーザーを使用。APIの対象外ロールは認証後コンテキストをスタブしてもよい。</x:v>
+        <x:v>R01などの試験ユーザーID・組織・権限は権限マトリクスに記入する。試験には既存ユーザーを使用する。APIの対象外ロールは、認証後のコンテキストをスタブして確認してもよい。</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="37.5" customHeight="1">
@@ -2903,12 +2853,12 @@
         <x:v>画面：docs/仕様/画面設計書_30分値データ登録画面.xlsx（画面定義書、画面処理内容説明書）。API：docs/仕様/機能定義書-LMMVMV-API-02_30分値一覧取得API.xlsx（機能定義、機能説明、データ項目更新仕様説明書）。</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="28" customHeight="1">
+    <x:row r="28" ht="37.5" customHeight="1">
       <x:c r="A28" s="6" t="str">
         <x:v>訂正済み項目</x:v>
       </x:c>
       <x:c r="B28" s="6" t="str">
-        <x:v>ARVE_OFFICE_CODE=事業所コード、ARVE_CUSTOMER_NUMBER=お客さま番号。ユーザー指示で設計書を訂正済み。</x:v>
+        <x:v>ARVE_OFFICE_CODEは事業所コード、ARVE_CUSTOMER_NUMBERはお客さま番号を示す。設計書のレスポンス項目名はユーザーの指示に従って訂正済みである。</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="37.5" customHeight="1">
